--- a/api/templates/no_stock/uk.xlsx
+++ b/api/templates/no_stock/uk.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\no_stock\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C014E430-9751-4912-84F6-60C99E449F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="NoStock" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="NoStock" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Пристрої зі статусом обслуговування встановлено на No-Stock</t>
   </si>
@@ -40,6 +29,9 @@
   </si>
   <si>
     <t>Сайти: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>* Дні, для яких встановлено значення «Немає в наявності», означають дні, коли пристрій було вручну позначено як «немає в наявності», а потім знову змінили свій статус</t>
@@ -72,36 +64,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -127,158 +119,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
+      <left style="medium"/>
+      <right style="medium"/>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{2AD35193-863D-48F7-808C-CC6E8650CF54}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFD7E4BD"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -586,85 +480,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.296875" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.19921875" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6" t="s">
+    <row r="11" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>13</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -674,6 +573,6 @@
     <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/no_stock/uk.xlsx
+++ b/api/templates/no_stock/uk.xlsx
@@ -150,12 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -517,7 +518,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -535,34 +536,34 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/api/templates/no_stock/uk.xlsx
+++ b/api/templates/no_stock/uk.xlsx
@@ -31,7 +31,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>* Дні, для яких встановлено значення «Немає в наявності», означають дні, коли пристрій було вручну позначено як «немає в наявності», а потім знову змінили свій статус</t>
@@ -150,13 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -518,7 +517,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -536,34 +535,34 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>14</v>
       </c>
     </row>
